--- a/results/tables/03_env_driven_taxa_clusters/table4_lda_variable_importance.xlsx
+++ b/results/tables/03_env_driven_taxa_clusters/table4_lda_variable_importance.xlsx
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08953323127485668</v>
+        <v>0.08939338919300555</v>
       </c>
       <c r="C2" t="n">
-        <v>3.933025315815631</v>
+        <v>4.871630971859648</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05547101937226606</v>
+        <v>0.03244408829717915</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>*</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-0.9387216552039042</v>
+        <v>0.8825922833018105</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,17 +495,17 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06932681041199718</v>
+        <v>0.04614603128653383</v>
       </c>
       <c r="C3" t="n">
-        <v>3.045395508826084</v>
+        <v>2.514799329942758</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08999990997558638</v>
+        <v>0.1197850123982249</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7464187023365487</v>
+        <v>-0.6173369881471966</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -522,17 +522,17 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>Velocity  at bottom (m/sec)_Imputed</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0222435542047309</v>
+        <v>0.014331425457768</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9771172173196414</v>
+        <v>0.7810131908101229</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3298943984750125</v>
+        <v>0.3815287617583588</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.3865046112960211</v>
+        <v>0.3439538769830455</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -549,17 +549,17 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Velocity  at bottom (m/sec)_Imputed</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01605592620711815</v>
+        <v>0.0108498250866953</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7053064358596103</v>
+        <v>0.5912779950370231</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4068732434091384</v>
+        <v>0.4459425693637307</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-0.3467831326380895</v>
+        <v>-0.2865860191798014</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003107859767284338</v>
+        <v>0.00836693452156223</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1365223947431327</v>
+        <v>0.4559690344300483</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7140543775593173</v>
+        <v>0.5029690582616103</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-0.1492957291608794</v>
+        <v>-0.2272118806123229</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001072768966131288</v>
+        <v>0.002612629308155978</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04712470935917833</v>
+        <v>0.1423792740212693</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8294416514962312</v>
+        <v>0.7077008312416349</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>-0.09110036885955661</v>
+        <v>0.1347158427225447</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>

--- a/results/tables/03_env_driven_taxa_clusters/table4_lda_variable_importance.xlsx
+++ b/results/tables/03_env_driven_taxa_clusters/table4_lda_variable_importance.xlsx
@@ -425,207 +425,239 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Environmental Variable</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Delta Wilks' Lambda</t>
+          <t>Habitat variables</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>F-statistic</t>
+          <t>Significance level</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>p-value</t>
+          <t>Cluster C1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Significance</t>
+          <t>Cluster C2</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>LD1 Coefficient</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LD2 Coefficient</t>
+          <t>Cluster C3</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>MPS (Phi)</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.08939338919300555</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4.871630971859648</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.03244408829717915</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>p &lt; 0.001***</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.35 ± 0.12</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.8825922833018105</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
+          <t>-1.17 ± 0.08</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1.60 ± 0.14</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Measured Depth (m)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>p &gt; 0.05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.74 ± 0.34</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4.10 ± 0.84</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4.79 ± 0.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LOI (%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>p &gt; 0.05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.22 ± 0.08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.55 ± 0.18</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1.45 ± 0.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Temperature (oC)</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0.04614603128653383</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2.514799329942758</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.1197850123982249</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.6173369881471966</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Velocity  at bottom (m/sec)_Imputed</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.014331425457768</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.7810131908101229</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3815287617583588</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3439538769830455</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Measured Depth (m)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.0108498250866953</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.5912779950370231</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.4459425693637307</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>p &gt; 0.05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>19.64 ± 0.44</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.2865860191798014</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
+          <t>19.94 ± 0.26</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>21.25 ± 0.31</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>LOI (%)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.00836693452156223</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.4559690344300483</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.5029690582616103</v>
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Water DO Bottom (mg/L)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>p &gt; 0.05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9.64 ± 0.11</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.2272118806123229</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
+          <t>9.53 ± 0.25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9.13 ± 0.44</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Water DO Bottom (mg/L)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.002612629308155978</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.1423792740212693</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.7077008312416349</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.1347158427225447</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sample size (n)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Significance: *** p&lt;0.001, ** p&lt;0.01, * p&lt;0.05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
